--- a/data/trans_orig/IP3101-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3101-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18630</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35907</t>
+          <t>36252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>44983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35015</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48790</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71238</t>
+          <t>70885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>90033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34998</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49702</t>
+          <t>49372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35397</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70979</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97607</t>
+          <t>97748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45357</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>65151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>67270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98530</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127744</t>
+          <t>127200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117084</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142410</t>
+          <t>141351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108522</t>
+          <t>107386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133719</t>
+          <t>133147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>230309</t>
+          <t>231401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267508</t>
+          <t>267579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27079</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39601</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38906</t>
+          <t>38901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37703</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71678</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>30781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37398</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>41902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>60702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92102</t>
+          <t>93105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118345</t>
+          <t>119089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58564</t>
+          <t>58934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47844</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>46651</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62928</t>
+          <t>63067</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87039</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>58118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96444</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93332</t>
+          <t>92726</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>69692</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91947</t>
+          <t>92475</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146664</t>
+          <t>147088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177769</t>
+          <t>178209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>52636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>54354</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70065</t>
+          <t>68388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98612</t>
+          <t>96368</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77491</t>
+          <t>77637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98871</t>
+          <t>99196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104322</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107819</t>
+          <t>107080</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>139084</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218005</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>263458</t>
+          <t>264686</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>111057</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>128858</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164514</t>
+          <t>164122</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>250777</t>
+          <t>251542</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>298084</t>
+          <t>298049</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>279828</t>
+          <t>281288</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>320461</t>
+          <t>320540</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278362</t>
+          <t>276220</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>319354</t>
+          <t>317766</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>571790</t>
+          <t>568474</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>631468</t>
+          <t>625617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>61163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75850</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59077</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>73070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124138</t>
+          <t>125549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143793</t>
+          <t>144469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>41225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>32472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61495</t>
+          <t>61371</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87355</t>
+          <t>87039</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49807</t>
+          <t>50088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64011</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78552</t>
+          <t>77172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107832</t>
+          <t>106777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133039</t>
+          <t>131693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156467</t>
+          <t>156028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142332</t>
+          <t>142657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168413</t>
+          <t>169158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281769</t>
+          <t>282811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319624</t>
+          <t>320039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20503</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35808</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42189</t>
+          <t>42804</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41887</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63403</t>
+          <t>62387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>73684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95763</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80564</t>
+          <t>78667</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101079</t>
+          <t>100590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160621</t>
+          <t>160765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189073</t>
+          <t>189865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>32867</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>29296</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>47965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44288</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>64024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87152</t>
+          <t>89204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68020</t>
+          <t>68249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75622</t>
+          <t>75124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96533</t>
+          <t>96522</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>65223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87179</t>
+          <t>86562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146771</t>
+          <t>147109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177701</t>
+          <t>177505</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34228</t>
+          <t>34647</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40200</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81460</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>111356</t>
+          <t>111312</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>121122</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>99467</t>
+          <t>97450</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>132636</t>
+          <t>132219</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>197765</t>
+          <t>197069</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>242996</t>
+          <t>239843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>91921</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>121819</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>97089</t>
+          <t>96117</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>129410</t>
+          <t>130488</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>197594</t>
+          <t>193966</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>242001</t>
+          <t>242135</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>361613</t>
+          <t>361213</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>404971</t>
+          <t>404376</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>366242</t>
+          <t>367532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>408740</t>
+          <t>409263</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>740109</t>
+          <t>742663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>801221</t>
+          <t>805533</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22284</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57875</t>
+          <t>58665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>70746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47616</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60631</t>
+          <t>60188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109876</t>
+          <t>108263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127077</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32100</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64351</t>
+          <t>64623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46473</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67806</t>
+          <t>67140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95870</t>
+          <t>96554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125516</t>
+          <t>126051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107985</t>
+          <t>108328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131575</t>
+          <t>130236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141741</t>
+          <t>141054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167158</t>
+          <t>167151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255378</t>
+          <t>257188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290317</t>
+          <t>289339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>30576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46515</t>
+          <t>47242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27079</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>61372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86988</t>
+          <t>86376</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51566</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>51469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70093</t>
+          <t>70144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97476</t>
+          <t>97861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81259</t>
+          <t>81725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103644</t>
+          <t>105051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76134</t>
+          <t>76842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164487</t>
+          <t>165256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196883</t>
+          <t>196219</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>23364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41472</t>
+          <t>41158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47606</t>
+          <t>47635</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37297</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53555</t>
+          <t>53947</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78731</t>
+          <t>79271</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49088</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64257</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91173</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>66203</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87798</t>
+          <t>88089</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68206</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89209</t>
+          <t>89068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140135</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170349</t>
+          <t>173161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>54521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>94802</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87713</t>
+          <t>89453</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>84749</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>115536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>182671</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>225981</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>165613</t>
+          <t>165816</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>134215</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>169797</t>
+          <t>173362</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>273208</t>
+          <t>277444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>324835</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -11196,47 +11196,47 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>332376</t>
+          <t>333778</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>374509</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>54,1%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>375301</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>375301</t>
-        </is>
-      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>353209</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>398210</t>
+          <t>396658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>698054</t>
+          <t>697862</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>760756</t>
+          <t>761185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
